--- a/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente</t>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,66; 100,0</t>
+          <t>63,44; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,95; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,09; 100,0</t>
+          <t>83,71; 100,0</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,01; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,1; 100,0</t>
+          <t>85,9; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,21; 100,0</t>
+          <t>92,66; 100,0</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,93; 94,98</t>
+          <t>43,46; 94,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,82; 100,0</t>
+          <t>27,35; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,13; 92,31</t>
+          <t>49,17; 91,0</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,7; 100,0</t>
+          <t>71,64; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,45; 100,0</t>
+          <t>84,46; 100,0</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,72; 95,55</t>
+          <t>78,94; 95,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,56; 99,12</t>
+          <t>87,44; 99,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 96,29</t>
+          <t>86,76; 96,7</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11128</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15941</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3335; 5258</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13717; 16386</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12364</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14471</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26835</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12758; 14852</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25217; 27216</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7806</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4792</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12598</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4582; 10001</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1695; 6200</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8232; 15235</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12467</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12297</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24763</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9825; 13713</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>21967; 26009</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>37450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>80137</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33060; 40102</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38889; 44090</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>74918; 83506</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 100,0</t>
+          <t>63,25; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,71; 100,0</t>
+          <t>82,81; 100,0</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,9; 100,0</t>
+          <t>84,36; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,66; 100,0</t>
+          <t>92,61; 100,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,46; 94,86</t>
+          <t>42,95; 95,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,35; 100,0</t>
+          <t>39,61; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,17; 91,0</t>
+          <t>50,9; 91,82</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,64; 100,0</t>
+          <t>72,29; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,46; 100,0</t>
+          <t>84,97; 100,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,94; 95,76</t>
+          <t>79,97; 95,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,44; 99,13</t>
+          <t>86,39; 99,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,7</t>
+          <t>87,28; 96,68</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3335; 5258</t>
+          <t>3326; 5258</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13717; 16386</t>
+          <t>13570; 16386</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12758; 14852</t>
+          <t>12529; 14852</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25217; 27216</t>
+          <t>25203; 27216</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4582; 10001</t>
+          <t>4528; 10050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1695; 6200</t>
+          <t>2456; 6200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8232; 15235</t>
+          <t>8522; 15373</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9825; 13713</t>
+          <t>9913; 13713</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21967; 26009</t>
+          <t>22101; 26009</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33060; 40102</t>
+          <t>33489; 40057</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38889; 44090</t>
+          <t>38422; 44091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74918; 83506</t>
+          <t>75373; 83490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65,51; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,81; 100,0</t>
+          <t>88,0; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81,87; 100,0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>84,36; 100,0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,61; 100,0</t>
+          <t>93,14; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,95; 95,32</t>
+          <t>33,31; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,61; 100,0</t>
+          <t>32,24; 89,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,9; 91,82</t>
+          <t>47,81; 89,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,29; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,84; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,97; 100,0</t>
+          <t>84,61; 100,0</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,97; 95,65</t>
+          <t>86,01; 99,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,39; 99,13</t>
+          <t>79,35; 95,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,28; 96,68</t>
+          <t>86,83; 96,34</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>14780</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3326; 5258</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3376; 5153</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13570; 16386</t>
+          <t>13322; 15139</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>25982</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>11479; 14021</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12529; 14852</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25203; 27216</t>
+          <t>24492; 26295</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>10146</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4528; 10050</t>
+          <t>1961; 5887</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2456; 6200</t>
+          <t>2663; 7427</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8522; 15373</t>
+          <t>6764; 12599</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>24835</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9913; 13713</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9844; 14095</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22101; 26009</t>
+          <t>22059; 26071</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33489; 40057</t>
+          <t>36010; 41558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38422; 44091</t>
+          <t>31567; 37926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75373; 83490</t>
+          <t>70902; 78667</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65,51; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88,0; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>81,87; 100,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>93,14; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>67,14%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>33,31; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32,24; 89,9</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>47,81; 89,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>69,84; 100,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84,61; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>86,01; 99,26</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>79,35; 95,33</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>86,83; 96,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9303413358816014</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9762890743222357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>9986</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14780</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.6551365221521842</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.879973504326355</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3376; 5153</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13322; 15139</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,47 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9776502876195881</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9880827908913049</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13708</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12274</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25982</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8186917756021203</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>0.9314145353395477</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11479; 14021</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24492; 26295</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +654,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7813941604133063</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6713717430090689</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7171501653329764</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3331488762754596</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3224056137235551</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4781206811958458</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1961; 5887</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2663; 7427</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6764; 12599</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8990062191284219</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8905326922816303</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +709,47 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9122903433137389</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9525808119932394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11976</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12859</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24835</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>0.6984212648671672</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8461260103833356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9844; 14095</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>22059; 26071</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +760,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9617813393191524</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8916626294165131</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9276177273610036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>40269</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>35473</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>75743</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8600731094049333</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.7934873386867402</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8683373196577306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>36010; 41558</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>31567; 37926</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>70902; 78667</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9925680317576339</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9533162452234279</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9634319325998786</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +825,437 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>9986</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4794</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>14780</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>3376</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13322</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>5153</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>15139</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>13708</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>12274</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>25982</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11479</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="n">
+        <v>24492</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>14021</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="n">
+        <v>26295</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4600</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5546</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>10146</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>6764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5887</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7427</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>12599</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11976</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>12859</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>24835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="n">
+        <v>9844</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>22059</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="n">
+        <v>14095</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>26071</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>35473</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>75743</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>36010</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>31567</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>70902</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>41558</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>37926</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>78667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>